--- a/outputs/tables/tabla_05_margenes_escenarios.xlsx
+++ b/outputs/tables/tabla_05_margenes_escenarios.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="margenes_escenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,22 +444,57 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>grado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_importado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ratio_costo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>ingreso_cop</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>costo_total_cop</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>costo_importado_cop</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>margen_cop</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>margen_pct</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>margen_pct_min</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>margen_pct_max</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>margen_pct_factor_060</t>
         </is>
       </c>
     </row>
@@ -481,23 +516,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F2" t="n">
-        <v>13174.81311303553</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>8135.412926987981</v>
+        <v>0.25</v>
       </c>
       <c r="H2" t="n">
-        <v>5039.400186047544</v>
+        <v>0.62</v>
       </c>
       <c r="I2" t="n">
-        <v>38.25025936088172</v>
+        <v>24474.98275334492</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17968.8752352061</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3768.492081185129</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6506.107518138819</v>
+      </c>
+      <c r="M2" t="n">
+        <v>26.58268479167631</v>
+      </c>
+      <c r="N2" t="n">
+        <v>15.72924688168051</v>
+      </c>
+      <c r="O2" t="n">
+        <v>39.60681028367127</v>
+      </c>
+      <c r="P2" t="n">
+        <v>28.75337237367547</v>
       </c>
     </row>
     <row r="3">
@@ -518,23 +576,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F3" t="n">
-        <v>14492.29442433908</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G3" t="n">
-        <v>8135.412926987981</v>
+        <v>0.25</v>
       </c>
       <c r="H3" t="n">
-        <v>6356.8814973511</v>
+        <v>0.62</v>
       </c>
       <c r="I3" t="n">
-        <v>43.86387214625613</v>
+        <v>27476.20732599355</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18599.13239546231</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4233.681889945667</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8877.074930531235</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32.30822516808272</v>
+      </c>
+      <c r="N3" t="n">
+        <v>22.36723280867265</v>
+      </c>
+      <c r="O3" t="n">
+        <v>44.2374159993748</v>
+      </c>
+      <c r="P3" t="n">
+        <v>34.29642363996474</v>
       </c>
     </row>
     <row r="4">
@@ -555,23 +636,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11198.5911460802</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>8135.412926987981</v>
+        <v>0.25</v>
       </c>
       <c r="H4" t="n">
-        <v>3063.178219092215</v>
+        <v>0.62</v>
       </c>
       <c r="I4" t="n">
-        <v>27.35324630691968</v>
+        <v>31198.94614995836</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19380.90754849492</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4810.706407660213</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11818.03860146344</v>
+      </c>
+      <c r="M4" t="n">
+        <v>37.8796083196522</v>
+      </c>
+      <c r="N4" t="n">
+        <v>28.8264943844702</v>
+      </c>
+      <c r="O4" t="n">
+        <v>48.7433450418706</v>
+      </c>
+      <c r="P4" t="n">
+        <v>39.69023110668861</v>
       </c>
     </row>
     <row r="5">
@@ -592,23 +696,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F5" t="n">
-        <v>13174.81311303553</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G5" t="n">
-        <v>9069.123925321315</v>
+        <v>0.25</v>
       </c>
       <c r="H5" t="n">
-        <v>4105.68918771421</v>
+        <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>31.16316833103255</v>
+        <v>25131.67118667825</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18625.56366853943</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3768.492081185129</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6506.107518138819</v>
+      </c>
+      <c r="M5" t="n">
+        <v>25.88808149609869</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15.318242996761</v>
+      </c>
+      <c r="O5" t="n">
+        <v>38.57188769530391</v>
+      </c>
+      <c r="P5" t="n">
+        <v>28.00204919596623</v>
       </c>
     </row>
     <row r="6">
@@ -629,23 +756,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F6" t="n">
-        <v>14492.29442433908</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G6" t="n">
-        <v>9069.123925321315</v>
+        <v>0.25</v>
       </c>
       <c r="H6" t="n">
-        <v>5423.170499017766</v>
+        <v>0.62</v>
       </c>
       <c r="I6" t="n">
-        <v>37.42106211912051</v>
+        <v>28132.89575932688</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19255.82082879564</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4233.681889945667</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8877.074930531235</v>
+      </c>
+      <c r="M6" t="n">
+        <v>31.55407465507075</v>
+      </c>
+      <c r="N6" t="n">
+        <v>21.84512860735666</v>
+      </c>
+      <c r="O6" t="n">
+        <v>43.20480991232763</v>
+      </c>
+      <c r="P6" t="n">
+        <v>33.49586386461355</v>
       </c>
     </row>
     <row r="7">
@@ -666,23 +816,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F7" t="n">
-        <v>11198.5911460802</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G7" t="n">
-        <v>9069.123925321315</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="n">
-        <v>2129.467220758881</v>
+        <v>0.62</v>
       </c>
       <c r="I7" t="n">
-        <v>19.01549215415594</v>
+        <v>31855.63458329169</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20037.59598182826</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4810.706407660213</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11818.03860146344</v>
+      </c>
+      <c r="M7" t="n">
+        <v>37.09873859383735</v>
+      </c>
+      <c r="N7" t="n">
+        <v>28.23225020495671</v>
+      </c>
+      <c r="O7" t="n">
+        <v>47.73852466049415</v>
+      </c>
+      <c r="P7" t="n">
+        <v>38.87203627161349</v>
       </c>
     </row>
     <row r="8">
@@ -703,23 +876,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F8" t="n">
-        <v>362.307360608477</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G8" t="n">
-        <v>447.9094755317528</v>
+        <v>0.15</v>
       </c>
       <c r="H8" t="n">
-        <v>-85.60211492327585</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>-23.62693233157378</v>
+        <v>320.2173139347174</v>
+      </c>
+      <c r="J8" t="n">
+        <v>318.626219456832</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34.89704502667647</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.591094477885406</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4968795904052152</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-8.94735354547915</v>
+      </c>
+      <c r="O8" t="n">
+        <v>14.66322929423178</v>
+      </c>
+      <c r="P8" t="n">
+        <v>24.10746243011616</v>
       </c>
     </row>
     <row r="9">
@@ -740,23 +936,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F9" t="n">
-        <v>398.5380966693247</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G9" t="n">
-        <v>447.9094755317528</v>
+        <v>0.15</v>
       </c>
       <c r="H9" t="n">
-        <v>-49.37137886242812</v>
+        <v>0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>-12.3881203014307</v>
+        <v>354.0036465934201</v>
+      </c>
+      <c r="J9" t="n">
+        <v>324.7922251670452</v>
+      </c>
+      <c r="K9" t="n">
+        <v>39.20480244066107</v>
+      </c>
+      <c r="L9" t="n">
+        <v>29.2114214263749</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.251728960273894</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.4343015242249316</v>
+      </c>
+      <c r="O9" t="n">
+        <v>21.28077468702217</v>
+      </c>
+      <c r="P9" t="n">
+        <v>29.966805171521</v>
       </c>
     </row>
     <row r="10">
@@ -777,23 +996,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F10" t="n">
-        <v>307.9612565172054</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G10" t="n">
-        <v>447.9094755317528</v>
+        <v>0.15</v>
       </c>
       <c r="H10" t="n">
-        <v>-139.9482190145474</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-45.44344980185151</v>
+        <v>395.9124372431456</v>
+      </c>
+      <c r="J10" t="n">
+        <v>332.4405794606201</v>
+      </c>
+      <c r="K10" t="n">
+        <v>44.54817324850107</v>
+      </c>
+      <c r="L10" t="n">
+        <v>63.47185778252543</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16.03179183369398</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.106429160680095</v>
+      </c>
+      <c r="O10" t="n">
+        <v>27.91983584321486</v>
+      </c>
+      <c r="P10" t="n">
+        <v>35.84519851622878</v>
       </c>
     </row>
     <row r="11">
@@ -814,23 +1056,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F11" t="n">
-        <v>362.307360608477</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G11" t="n">
-        <v>1381.620473865086</v>
+        <v>0.15</v>
       </c>
       <c r="H11" t="n">
-        <v>-1019.313113256609</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-281.3393334169983</v>
+        <v>341.9243139347174</v>
+      </c>
+      <c r="J11" t="n">
+        <v>340.333219456832</v>
+      </c>
+      <c r="K11" t="n">
+        <v>34.89704502667647</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.591094477885406</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4653352841673579</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-8.379332508376777</v>
+      </c>
+      <c r="O11" t="n">
+        <v>13.73233697298358</v>
+      </c>
+      <c r="P11" t="n">
+        <v>22.57700476552771</v>
       </c>
     </row>
     <row r="12">
@@ -851,23 +1116,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F12" t="n">
-        <v>398.5380966693247</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G12" t="n">
-        <v>1381.620473865086</v>
+        <v>0.15</v>
       </c>
       <c r="H12" t="n">
-        <v>-983.0823771957616</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="n">
-        <v>-246.6721212881802</v>
+        <v>375.7106465934201</v>
+      </c>
+      <c r="J12" t="n">
+        <v>346.4992251670452</v>
+      </c>
+      <c r="K12" t="n">
+        <v>39.20480244066107</v>
+      </c>
+      <c r="L12" t="n">
+        <v>29.2114214263749</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7.774978348693535</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.4092093867733344</v>
+      </c>
+      <c r="O12" t="n">
+        <v>20.05125995189387</v>
+      </c>
+      <c r="P12" t="n">
+        <v>28.23544768736074</v>
       </c>
     </row>
     <row r="13">
@@ -888,23 +1176,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F13" t="n">
-        <v>307.9612565172054</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G13" t="n">
-        <v>1381.620473865086</v>
+        <v>0.15</v>
       </c>
       <c r="H13" t="n">
-        <v>-1073.659217347881</v>
+        <v>0.85</v>
       </c>
       <c r="I13" t="n">
-        <v>-348.6345099023509</v>
+        <v>417.6194372431456</v>
+      </c>
+      <c r="J13" t="n">
+        <v>354.1475794606201</v>
+      </c>
+      <c r="K13" t="n">
+        <v>44.54817324850107</v>
+      </c>
+      <c r="L13" t="n">
+        <v>63.47185778252543</v>
+      </c>
+      <c r="M13" t="n">
+        <v>15.19849224488346</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.685073634336545</v>
+      </c>
+      <c r="O13" t="n">
+        <v>26.46862016070387</v>
+      </c>
+      <c r="P13" t="n">
+        <v>33.98203877125082</v>
       </c>
     </row>
     <row r="14">
@@ -925,23 +1236,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4940.554917388322</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G14" t="n">
-        <v>3194.85800959966</v>
+        <v>0.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1745.696907788662</v>
+        <v>0.75</v>
       </c>
       <c r="I14" t="n">
-        <v>35.33402496235125</v>
+        <v>4164.652592039076</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3678.732684246563</v>
+      </c>
+      <c r="K14" t="n">
+        <v>839.7684632087922</v>
+      </c>
+      <c r="L14" t="n">
+        <v>485.9199077925132</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11.66771770402581</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.93146697490095</v>
+      </c>
+      <c r="O14" t="n">
+        <v>21.40396843315066</v>
+      </c>
+      <c r="P14" t="n">
+        <v>26.2720937977131</v>
       </c>
     </row>
     <row r="15">
@@ -962,23 +1296,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5434.610409127155</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G15" t="n">
-        <v>3194.85800959966</v>
+        <v>0.3</v>
       </c>
       <c r="H15" t="n">
-        <v>2239.752399527496</v>
+        <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>41.21274996577388</v>
+        <v>4625.375310112296</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3807.735045307065</v>
+      </c>
+      <c r="K15" t="n">
+        <v>943.4310747752666</v>
+      </c>
+      <c r="L15" t="n">
+        <v>817.6402648052308</v>
+      </c>
+      <c r="M15" t="n">
+        <v>17.67727395045441</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8.612005257913703</v>
+      </c>
+      <c r="O15" t="n">
+        <v>26.74254264299514</v>
+      </c>
+      <c r="P15" t="n">
+        <v>31.2751769892655</v>
       </c>
     </row>
     <row r="16">
@@ -999,23 +1356,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4199.471679780074</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G16" t="n">
-        <v>3194.85800959966</v>
+        <v>0.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1004.613670180414</v>
+        <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>23.92238230864854</v>
+        <v>5196.858818972188</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3967.750427787835</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1072.014864268742</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1229.108391184353</v>
+      </c>
+      <c r="M16" t="n">
+        <v>23.65098675948716</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15.25269809379212</v>
+      </c>
+      <c r="O16" t="n">
+        <v>32.04927542518221</v>
+      </c>
+      <c r="P16" t="n">
+        <v>36.24841975802975</v>
       </c>
     </row>
     <row r="17">
@@ -1036,23 +1416,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4940.554917388322</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G17" t="n">
-        <v>4128.569007932993</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="n">
-        <v>811.9859094553285</v>
+        <v>0.75</v>
       </c>
       <c r="I17" t="n">
-        <v>16.43511554942012</v>
+        <v>5915.821747594631</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5429.901839802118</v>
+      </c>
+      <c r="K17" t="n">
+        <v>839.7684632087922</v>
+      </c>
+      <c r="L17" t="n">
+        <v>485.9199077925132</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8.213903807870611</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.359724698725019</v>
+      </c>
+      <c r="O17" t="n">
+        <v>15.06808291701617</v>
+      </c>
+      <c r="P17" t="n">
+        <v>18.49517247158895</v>
       </c>
     </row>
     <row r="18">
@@ -1073,23 +1476,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5434.610409127155</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G18" t="n">
-        <v>4128.569007932993</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="n">
-        <v>1306.041401194162</v>
+        <v>0.75</v>
       </c>
       <c r="I18" t="n">
-        <v>24.03192322674558</v>
+        <v>6376.544465667852</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5558.90420086262</v>
+      </c>
+      <c r="K18" t="n">
+        <v>943.4310747752666</v>
+      </c>
+      <c r="L18" t="n">
+        <v>817.6402648052317</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12.82262311832864</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.246918955083204</v>
+      </c>
+      <c r="O18" t="n">
+        <v>19.39832728157408</v>
+      </c>
+      <c r="P18" t="n">
+        <v>22.68617936319682</v>
       </c>
     </row>
     <row r="19">
@@ -1110,23 +1536,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4199.471679780074</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G19" t="n">
-        <v>4128.569007932993</v>
+        <v>0.3</v>
       </c>
       <c r="H19" t="n">
-        <v>70.90267184708046</v>
+        <v>0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>1.688371234611912</v>
+        <v>6948.027974527744</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5718.91958334339</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1072.014864268742</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1229.108391184354</v>
+      </c>
+      <c r="M19" t="n">
+        <v>17.69003227520679</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11.40843400349601</v>
+      </c>
+      <c r="O19" t="n">
+        <v>23.97163054691755</v>
+      </c>
+      <c r="P19" t="n">
+        <v>27.11242968277294</v>
       </c>
     </row>
     <row r="20">
@@ -1147,23 +1596,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10292.822744559</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G20" t="n">
-        <v>6406.218705902068</v>
+        <v>0.3</v>
       </c>
       <c r="H20" t="n">
-        <v>3886.604038656936</v>
+        <v>0.87</v>
       </c>
       <c r="I20" t="n">
-        <v>37.76033198192862</v>
+        <v>16458.43391859993</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16459.80332326033</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2029.440452754581</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1.369404660403234</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.008320382529565275</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-3.087904232695319</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.584527442663799</v>
+      </c>
+      <c r="P20" t="n">
+        <v>13.84980694321624</v>
       </c>
     </row>
     <row r="21">
@@ -1184,23 +1656,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F21" t="n">
-        <v>11322.10501901491</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G21" t="n">
-        <v>6406.218705902068</v>
+        <v>0.3</v>
       </c>
       <c r="H21" t="n">
-        <v>4915.886313112839</v>
+        <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>43.41848361993512</v>
+        <v>17418.2729145858</v>
+      </c>
+      <c r="J21" t="n">
+        <v>16763.11244599186</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2279.958430706894</v>
+      </c>
+      <c r="L21" t="n">
+        <v>655.1604685939383</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.761340012334498</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.7522680024669123</v>
+      </c>
+      <c r="O21" t="n">
+        <v>7.271924023846672</v>
+      </c>
+      <c r="P21" t="n">
+        <v>17.30216405673863</v>
       </c>
     </row>
     <row r="22">
@@ -1221,23 +1716,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F22" t="n">
-        <v>8748.899332875153</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G22" t="n">
-        <v>6406.218705902068</v>
+        <v>0.3</v>
       </c>
       <c r="H22" t="n">
-        <v>2342.680626973085</v>
+        <v>0.87</v>
       </c>
       <c r="I22" t="n">
-        <v>26.77686115521013</v>
+        <v>18608.86355804391</v>
+      </c>
+      <c r="J22" t="n">
+        <v>17139.33908932463</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2590.702588649461</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1469.524468719283</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7.896906031556466</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.965190159946594</v>
+      </c>
+      <c r="O22" t="n">
+        <v>11.31724121510127</v>
+      </c>
+      <c r="P22" t="n">
+        <v>21.08962745380076</v>
       </c>
     </row>
     <row r="23">
@@ -1258,23 +1776,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10292.822744559</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G23" t="n">
-        <v>7339.929704235402</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
-        <v>2952.893040323602</v>
+        <v>0.87</v>
       </c>
       <c r="I23" t="n">
-        <v>28.68885546372166</v>
+        <v>16458.43391859993</v>
+      </c>
+      <c r="J23" t="n">
+        <v>16459.80332326033</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2029.440452754581</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.369404660403234</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.008320382529565275</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-3.087904232695319</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.584527442663799</v>
+      </c>
+      <c r="P23" t="n">
+        <v>13.84980694321624</v>
       </c>
     </row>
     <row r="24">
@@ -1295,23 +1836,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F24" t="n">
-        <v>11322.10501901491</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G24" t="n">
-        <v>7339.929704235402</v>
+        <v>0.3</v>
       </c>
       <c r="H24" t="n">
-        <v>3982.175314779505</v>
+        <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>35.17168678520153</v>
+        <v>17418.2729145858</v>
+      </c>
+      <c r="J24" t="n">
+        <v>16763.11244599186</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2279.958430706894</v>
+      </c>
+      <c r="L24" t="n">
+        <v>655.1604685939383</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.761340012334498</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.7522680024669123</v>
+      </c>
+      <c r="O24" t="n">
+        <v>7.271924023846672</v>
+      </c>
+      <c r="P24" t="n">
+        <v>17.30216405673863</v>
       </c>
     </row>
     <row r="25">
@@ -1332,23 +1896,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F25" t="n">
-        <v>8748.899332875153</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G25" t="n">
-        <v>7339.929704235402</v>
+        <v>0.3</v>
       </c>
       <c r="H25" t="n">
-        <v>1408.969628639751</v>
+        <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>16.10453583967254</v>
+        <v>18608.86355804391</v>
+      </c>
+      <c r="J25" t="n">
+        <v>17139.33908932463</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2590.702588649461</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1469.524468719283</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7.896906031556466</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.965190159946594</v>
+      </c>
+      <c r="O25" t="n">
+        <v>11.31724121510127</v>
+      </c>
+      <c r="P25" t="n">
+        <v>21.08962745380076</v>
       </c>
     </row>
     <row r="26">
@@ -1369,23 +1956,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F26" t="n">
-        <v>115279.6147390609</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G26" t="n">
-        <v>69398.29390260318</v>
+        <v>0.65</v>
       </c>
       <c r="H26" t="n">
-        <v>45881.32083645767</v>
+        <v>0.55</v>
       </c>
       <c r="I26" t="n">
-        <v>39.80002964124363</v>
+        <v>87357.31758276363</v>
+      </c>
+      <c r="J26" t="n">
+        <v>55027.3260022231</v>
+      </c>
+      <c r="K26" t="n">
+        <v>31133.63821007411</v>
+      </c>
+      <c r="L26" t="n">
+        <v>32329.99158054053</v>
+      </c>
+      <c r="M26" t="n">
+        <v>37.00891061577138</v>
+      </c>
+      <c r="N26" t="n">
+        <v>21.40924399370883</v>
+      </c>
+      <c r="O26" t="n">
+        <v>52.60857723783396</v>
+      </c>
+      <c r="P26" t="n">
+        <v>31.80902174175053</v>
       </c>
     </row>
     <row r="27">
@@ -1406,23 +2016,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F27" t="n">
-        <v>126807.576212967</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G27" t="n">
-        <v>69398.29390260318</v>
+        <v>0.65</v>
       </c>
       <c r="H27" t="n">
-        <v>57409.28231036378</v>
+        <v>0.55</v>
       </c>
       <c r="I27" t="n">
-        <v>45.2727542193124</v>
+        <v>98107.51433780542</v>
+      </c>
+      <c r="J27" t="n">
+        <v>59461.78216367784</v>
+      </c>
+      <c r="K27" t="n">
+        <v>34976.83355000155</v>
+      </c>
+      <c r="L27" t="n">
+        <v>38645.73217412758</v>
+      </c>
+      <c r="M27" t="n">
+        <v>39.39120508247916</v>
+      </c>
+      <c r="N27" t="n">
+        <v>24.43251960811999</v>
+      </c>
+      <c r="O27" t="n">
+        <v>54.34989055683835</v>
+      </c>
+      <c r="P27" t="n">
+        <v>34.40497659102611</v>
       </c>
     </row>
     <row r="28">
@@ -1443,23 +2076,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F28" t="n">
-        <v>97987.67252820171</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G28" t="n">
-        <v>69398.29390260318</v>
+        <v>0.65</v>
       </c>
       <c r="H28" t="n">
-        <v>28589.37862559853</v>
+        <v>0.55</v>
       </c>
       <c r="I28" t="n">
-        <v>29.17650546028661</v>
+        <v>111442.1295445362</v>
+      </c>
+      <c r="J28" t="n">
+        <v>64962.31093645431</v>
+      </c>
+      <c r="K28" t="n">
+        <v>39743.95848640782</v>
+      </c>
+      <c r="L28" t="n">
+        <v>46479.81860808193</v>
+      </c>
+      <c r="M28" t="n">
+        <v>41.70758293837785</v>
+      </c>
+      <c r="N28" t="n">
+        <v>27.37214306079015</v>
+      </c>
+      <c r="O28" t="n">
+        <v>56.04302281596556</v>
+      </c>
+      <c r="P28" t="n">
+        <v>36.92910297918194</v>
       </c>
     </row>
     <row r="29">
@@ -1480,23 +2136,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F29" t="n">
-        <v>115279.6147390609</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G29" t="n">
-        <v>70332.00490093652</v>
+        <v>0.65</v>
       </c>
       <c r="H29" t="n">
-        <v>44947.60983812434</v>
+        <v>0.55</v>
       </c>
       <c r="I29" t="n">
-        <v>38.99007638068943</v>
+        <v>88451.79830498584</v>
+      </c>
+      <c r="J29" t="n">
+        <v>56121.80672444532</v>
+      </c>
+      <c r="K29" t="n">
+        <v>31133.63821007411</v>
+      </c>
+      <c r="L29" t="n">
+        <v>32329.99158054053</v>
+      </c>
+      <c r="M29" t="n">
+        <v>36.55097148965275</v>
+      </c>
+      <c r="N29" t="n">
+        <v>21.14433129235626</v>
+      </c>
+      <c r="O29" t="n">
+        <v>51.95761168694924</v>
+      </c>
+      <c r="P29" t="n">
+        <v>31.41542475722058</v>
       </c>
     </row>
     <row r="30">
@@ -1517,23 +2196,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F30" t="n">
-        <v>126807.576212967</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G30" t="n">
-        <v>70332.00490093652</v>
+        <v>0.65</v>
       </c>
       <c r="H30" t="n">
-        <v>56475.57131203044</v>
+        <v>0.55</v>
       </c>
       <c r="I30" t="n">
-        <v>44.53643307335404</v>
+        <v>99201.99506002764</v>
+      </c>
+      <c r="J30" t="n">
+        <v>60556.26288590006</v>
+      </c>
+      <c r="K30" t="n">
+        <v>34976.83355000155</v>
+      </c>
+      <c r="L30" t="n">
+        <v>38645.73217412757</v>
+      </c>
+      <c r="M30" t="n">
+        <v>38.95660782904905</v>
+      </c>
+      <c r="N30" t="n">
+        <v>24.1629592863722</v>
+      </c>
+      <c r="O30" t="n">
+        <v>53.75025637172591</v>
+      </c>
+      <c r="P30" t="n">
+        <v>34.02539164815677</v>
       </c>
     </row>
     <row r="31">
@@ -1554,23 +2256,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F31" t="n">
-        <v>97987.67252820171</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G31" t="n">
-        <v>70332.00490093652</v>
+        <v>0.65</v>
       </c>
       <c r="H31" t="n">
-        <v>27655.6676272652</v>
+        <v>0.55</v>
       </c>
       <c r="I31" t="n">
-        <v>28.22361927139932</v>
+        <v>112536.6102667584</v>
+      </c>
+      <c r="J31" t="n">
+        <v>66056.79165867652</v>
+      </c>
+      <c r="K31" t="n">
+        <v>39743.95848640782</v>
+      </c>
+      <c r="L31" t="n">
+        <v>46479.81860808193</v>
+      </c>
+      <c r="M31" t="n">
+        <v>41.30195364682256</v>
+      </c>
+      <c r="N31" t="n">
+        <v>27.10593384376353</v>
+      </c>
+      <c r="O31" t="n">
+        <v>55.4979734498816</v>
+      </c>
+      <c r="P31" t="n">
+        <v>36.56994704580288</v>
       </c>
     </row>
     <row r="32">
@@ -1591,23 +2316,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F32" t="n">
-        <v>27996.47786520049</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G32" t="n">
-        <v>17028.41177828696</v>
+        <v>0.55</v>
       </c>
       <c r="H32" t="n">
-        <v>10968.06608691353</v>
+        <v>0.74</v>
       </c>
       <c r="I32" t="n">
-        <v>39.17659264041493</v>
+        <v>21612.95459192513</v>
+      </c>
+      <c r="J32" t="n">
+        <v>18146.64488791798</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8607.937773246864</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3466.309704007155</v>
+      </c>
+      <c r="M32" t="n">
+        <v>16.03811125991174</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7.77470901392016</v>
+      </c>
+      <c r="O32" t="n">
+        <v>25.33443878665225</v>
+      </c>
+      <c r="P32" t="n">
+        <v>30.49906519039699</v>
       </c>
     </row>
     <row r="33">
@@ -1628,23 +2376,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F33" t="n">
-        <v>30796.12565172055</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G33" t="n">
-        <v>17028.41177828696</v>
+        <v>0.55</v>
       </c>
       <c r="H33" t="n">
-        <v>13767.71387343359</v>
+        <v>0.74</v>
       </c>
       <c r="I33" t="n">
-        <v>44.70599330946813</v>
+        <v>24223.71666100671</v>
+      </c>
+      <c r="J33" t="n">
+        <v>19352.81696383367</v>
+      </c>
+      <c r="K33" t="n">
+        <v>9670.517935363065</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4870.899697173041</v>
+      </c>
+      <c r="M33" t="n">
+        <v>20.10797833106182</v>
+      </c>
+      <c r="N33" t="n">
+        <v>12.26096239698893</v>
+      </c>
+      <c r="O33" t="n">
+        <v>28.93587125689385</v>
+      </c>
+      <c r="P33" t="n">
+        <v>33.84025621568941</v>
       </c>
     </row>
     <row r="34">
@@ -1665,23 +2436,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F34" t="n">
-        <v>23797.00618542042</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G34" t="n">
-        <v>17028.41177828696</v>
+        <v>0.55</v>
       </c>
       <c r="H34" t="n">
-        <v>6768.594407133456</v>
+        <v>0.74</v>
       </c>
       <c r="I34" t="n">
-        <v>28.44305016519403</v>
+        <v>27462.12321121277</v>
+      </c>
+      <c r="J34" t="n">
+        <v>20848.96079002886</v>
+      </c>
+      <c r="K34" t="n">
+        <v>10988.54940129693</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6613.162421183901</v>
+      </c>
+      <c r="M34" t="n">
+        <v>24.0810310634822</v>
+      </c>
+      <c r="N34" t="n">
+        <v>16.64049640886873</v>
+      </c>
+      <c r="O34" t="n">
+        <v>32.45163254992236</v>
+      </c>
+      <c r="P34" t="n">
+        <v>37.10196670905578</v>
       </c>
     </row>
     <row r="35">
@@ -1702,23 +2496,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F35" t="n">
-        <v>27996.47786520049</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G35" t="n">
-        <v>17962.12277662029</v>
+        <v>0.55</v>
       </c>
       <c r="H35" t="n">
-        <v>10034.3550885802</v>
+        <v>0.74</v>
       </c>
       <c r="I35" t="n">
-        <v>35.84149097930944</v>
+        <v>23489.2072585918</v>
+      </c>
+      <c r="J35" t="n">
+        <v>20022.89755458464</v>
+      </c>
+      <c r="K35" t="n">
+        <v>8607.937773246864</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3466.309704007155</v>
+      </c>
+      <c r="M35" t="n">
+        <v>14.75703145639051</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7.153686841509919</v>
+      </c>
+      <c r="O35" t="n">
+        <v>23.31079414813118</v>
+      </c>
+      <c r="P35" t="n">
+        <v>28.06288453243154</v>
       </c>
     </row>
     <row r="36">
@@ -1739,23 +2556,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F36" t="n">
-        <v>30796.12565172055</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G36" t="n">
-        <v>17962.12277662029</v>
+        <v>0.55</v>
       </c>
       <c r="H36" t="n">
-        <v>12834.00287510025</v>
+        <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>41.67408270846314</v>
+        <v>26099.96932767337</v>
+      </c>
+      <c r="J36" t="n">
+        <v>21229.06963050033</v>
+      </c>
+      <c r="K36" t="n">
+        <v>9670.517935363065</v>
+      </c>
+      <c r="L36" t="n">
+        <v>4870.899697173041</v>
+      </c>
+      <c r="M36" t="n">
+        <v>18.66247287888</v>
+      </c>
+      <c r="N36" t="n">
+        <v>11.37955663346342</v>
+      </c>
+      <c r="O36" t="n">
+        <v>26.85575365497366</v>
+      </c>
+      <c r="P36" t="n">
+        <v>31.40757630835902</v>
       </c>
     </row>
     <row r="37">
@@ -1776,23 +2616,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F37" t="n">
-        <v>23797.00618542042</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G37" t="n">
-        <v>17962.12277662029</v>
+        <v>0.55</v>
       </c>
       <c r="H37" t="n">
-        <v>5834.883408800124</v>
+        <v>0.74</v>
       </c>
       <c r="I37" t="n">
-        <v>24.51940115212875</v>
+        <v>29338.37587787943</v>
+      </c>
+      <c r="J37" t="n">
+        <v>22725.21345669553</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10988.54940129693</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6613.162421183901</v>
+      </c>
+      <c r="M37" t="n">
+        <v>22.54099698194301</v>
+      </c>
+      <c r="N37" t="n">
+        <v>15.57630063021496</v>
+      </c>
+      <c r="O37" t="n">
+        <v>30.3762803776371</v>
+      </c>
+      <c r="P37" t="n">
+        <v>34.72921559746715</v>
       </c>
     </row>
     <row r="38">
@@ -1813,23 +2676,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F38" t="n">
-        <v>8645.971105429564</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G38" t="n">
-        <v>5418.107722424405</v>
+        <v>0.4</v>
       </c>
       <c r="H38" t="n">
-        <v>3227.863383005159</v>
+        <v>0.79</v>
       </c>
       <c r="I38" t="n">
-        <v>37.33372854991501</v>
+        <v>6693.663108290605</v>
+      </c>
+      <c r="J38" t="n">
+        <v>6063.445066730631</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2063.964267353165</v>
+      </c>
+      <c r="L38" t="n">
+        <v>630.2180415599742</v>
+      </c>
+      <c r="M38" t="n">
+        <v>9.415144314320237</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.01730262675851245</v>
+      </c>
+      <c r="O38" t="n">
+        <v>18.84759125539899</v>
+      </c>
+      <c r="P38" t="n">
+        <v>29.32808785659759</v>
       </c>
     </row>
     <row r="39">
@@ -1850,23 +2736,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F39" t="n">
-        <v>9510.568215972522</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G39" t="n">
-        <v>5418.107722424405</v>
+        <v>0.4</v>
       </c>
       <c r="H39" t="n">
-        <v>4092.460493548117</v>
+        <v>0.79</v>
       </c>
       <c r="I39" t="n">
-        <v>43.03066231810456</v>
+        <v>7499.92786491874</v>
+      </c>
+      <c r="J39" t="n">
+        <v>6362.569291439669</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2318.743930447655</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1137.358573479071</v>
+      </c>
+      <c r="M39" t="n">
+        <v>15.16492683615157</v>
+      </c>
+      <c r="N39" t="n">
+        <v>6.3594854474184</v>
+      </c>
+      <c r="O39" t="n">
+        <v>23.97036822488475</v>
+      </c>
+      <c r="P39" t="n">
+        <v>33.75419199014382</v>
       </c>
     </row>
     <row r="40">
@@ -1887,23 +2796,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F40" t="n">
-        <v>7349.075439615129</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G40" t="n">
-        <v>5418.107722424405</v>
+        <v>0.4</v>
       </c>
       <c r="H40" t="n">
-        <v>1930.967717190724</v>
+        <v>0.79</v>
       </c>
       <c r="I40" t="n">
-        <v>26.27497476460589</v>
+        <v>8500.024005423551</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6733.604959566954</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2634.774310847175</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1766.419045856597</v>
+      </c>
+      <c r="M40" t="n">
+        <v>20.78134184949961</v>
+      </c>
+      <c r="N40" t="n">
+        <v>12.58836247724714</v>
+      </c>
+      <c r="O40" t="n">
+        <v>28.97432122175209</v>
+      </c>
+      <c r="P40" t="n">
+        <v>38.07763163536594</v>
       </c>
     </row>
     <row r="41">
@@ -1924,23 +2856,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F41" t="n">
-        <v>8645.971105429564</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G41" t="n">
-        <v>6351.818720757738</v>
+        <v>0.4</v>
       </c>
       <c r="H41" t="n">
-        <v>2294.152384671826</v>
+        <v>0.79</v>
       </c>
       <c r="I41" t="n">
-        <v>26.53435174252579</v>
+        <v>7350.351541623939</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6720.133500063965</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2063.964267353165</v>
+      </c>
+      <c r="L41" t="n">
+        <v>630.2180415599742</v>
+      </c>
+      <c r="M41" t="n">
+        <v>8.573985039914675</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-0.01575679118938965</v>
+      </c>
+      <c r="O41" t="n">
+        <v>17.16372687101874</v>
+      </c>
+      <c r="P41" t="n">
+        <v>26.70788446113436</v>
       </c>
     </row>
     <row r="42">
@@ -1961,23 +2916,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F42" t="n">
-        <v>9510.568215972522</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G42" t="n">
-        <v>6351.818720757738</v>
+        <v>0.4</v>
       </c>
       <c r="H42" t="n">
-        <v>3158.749495214784</v>
+        <v>0.79</v>
       </c>
       <c r="I42" t="n">
-        <v>33.21304703865982</v>
+        <v>8156.616298252074</v>
+      </c>
+      <c r="J42" t="n">
+        <v>7019.257724773002</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2318.743930447655</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1137.358573479071</v>
+      </c>
+      <c r="M42" t="n">
+        <v>13.94399996139088</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.847483854776822</v>
+      </c>
+      <c r="O42" t="n">
+        <v>22.04051606800495</v>
+      </c>
+      <c r="P42" t="n">
+        <v>31.0366450753539</v>
       </c>
     </row>
     <row r="43">
@@ -1998,23 +2976,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F43" t="n">
-        <v>7349.075439615129</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G43" t="n">
-        <v>6351.818720757738</v>
+        <v>0.4</v>
       </c>
       <c r="H43" t="n">
-        <v>997.2567188573903</v>
+        <v>0.79</v>
       </c>
       <c r="I43" t="n">
-        <v>13.56982557944209</v>
+        <v>9156.712438756884</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7390.293392900287</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2634.774310847175</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1766.419045856596</v>
+      </c>
+      <c r="M43" t="n">
+        <v>19.29097432807888</v>
+      </c>
+      <c r="N43" t="n">
+        <v>11.6855677145301</v>
+      </c>
+      <c r="O43" t="n">
+        <v>26.89638094162767</v>
+      </c>
+      <c r="P43" t="n">
+        <v>35.34683273445965</v>
       </c>
     </row>
     <row r="44">
@@ -2035,23 +3036,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F44" t="n">
-        <v>22644.21003802981</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G44" t="n">
-        <v>13817.05108198455</v>
+        <v>0.55</v>
       </c>
       <c r="H44" t="n">
-        <v>8827.158956045258</v>
+        <v>0.79</v>
       </c>
       <c r="I44" t="n">
-        <v>38.98196908269482</v>
+        <v>17538.74293203095</v>
+      </c>
+      <c r="J44" t="n">
+        <v>15637.94184454893</v>
+      </c>
+      <c r="K44" t="n">
+        <v>7432.728462789672</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1900.801087482025</v>
+      </c>
+      <c r="M44" t="n">
+        <v>10.8377270528927</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.60149926989962</v>
+      </c>
+      <c r="O44" t="n">
+        <v>20.10348330875993</v>
+      </c>
+      <c r="P44" t="n">
+        <v>30.39876803750127</v>
       </c>
     </row>
     <row r="45">
@@ -2072,23 +3096,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F45" t="n">
-        <v>24908.6310418328</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G45" t="n">
-        <v>13817.05108198455</v>
+        <v>0.55</v>
       </c>
       <c r="H45" t="n">
-        <v>11091.57995984824</v>
+        <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>44.52906280244984</v>
+        <v>19650.38872319987</v>
+      </c>
+      <c r="J45" t="n">
+        <v>16671.59245932612</v>
+      </c>
+      <c r="K45" t="n">
+        <v>8350.238559052568</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2978.796263873759</v>
+      </c>
+      <c r="M45" t="n">
+        <v>15.15896863840102</v>
+      </c>
+      <c r="N45" t="n">
+        <v>7.334984825032759</v>
+      </c>
+      <c r="O45" t="n">
+        <v>23.96095042844032</v>
+      </c>
+      <c r="P45" t="n">
+        <v>33.74093019515065</v>
       </c>
     </row>
     <row r="46">
@@ -2109,23 +3156,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F46" t="n">
-        <v>19247.57853232534</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G46" t="n">
-        <v>13817.05108198455</v>
+        <v>0.55</v>
       </c>
       <c r="H46" t="n">
-        <v>5430.527450340784</v>
+        <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>28.2140812737586</v>
+        <v>22269.68813880771</v>
+      </c>
+      <c r="J46" t="n">
+        <v>17953.73952326615</v>
+      </c>
+      <c r="K46" t="n">
+        <v>9488.324155134174</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4315.948615541558</v>
+      </c>
+      <c r="M46" t="n">
+        <v>19.38037294747958</v>
+      </c>
+      <c r="N46" t="n">
+        <v>11.95910868480756</v>
+      </c>
+      <c r="O46" t="n">
+        <v>27.72929524298561</v>
+      </c>
+      <c r="P46" t="n">
+        <v>37.00587557132563</v>
       </c>
     </row>
     <row r="47">
@@ -2146,23 +3216,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F47" t="n">
-        <v>22644.21003802981</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G47" t="n">
-        <v>14750.76208031789</v>
+        <v>0.55</v>
       </c>
       <c r="H47" t="n">
-        <v>7893.447957711924</v>
+        <v>0.79</v>
       </c>
       <c r="I47" t="n">
-        <v>34.85857066532802</v>
+        <v>19289.91208758651</v>
+      </c>
+      <c r="J47" t="n">
+        <v>17389.11100010448</v>
+      </c>
+      <c r="K47" t="n">
+        <v>7432.728462789672</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1900.801087482025</v>
+      </c>
+      <c r="M47" t="n">
+        <v>9.853860809999404</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.365330994017213</v>
+      </c>
+      <c r="O47" t="n">
+        <v>18.27845685297938</v>
+      </c>
+      <c r="P47" t="n">
+        <v>27.63911912295711</v>
       </c>
     </row>
     <row r="48">
@@ -2183,23 +3276,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F48" t="n">
-        <v>24908.6310418328</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G48" t="n">
-        <v>14750.76208031789</v>
+        <v>0.55</v>
       </c>
       <c r="H48" t="n">
-        <v>10157.86896151491</v>
+        <v>0.79</v>
       </c>
       <c r="I48" t="n">
-        <v>40.78051878666185</v>
+        <v>21401.55787875543</v>
+      </c>
+      <c r="J48" t="n">
+        <v>18422.76161488167</v>
+      </c>
+      <c r="K48" t="n">
+        <v>8350.238559052568</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2978.796263873759</v>
+      </c>
+      <c r="M48" t="n">
+        <v>13.91859546276631</v>
+      </c>
+      <c r="N48" t="n">
+        <v>6.734804256177254</v>
+      </c>
+      <c r="O48" t="n">
+        <v>22.00036057017901</v>
+      </c>
+      <c r="P48" t="n">
+        <v>30.98009957841534</v>
       </c>
     </row>
     <row r="49">
@@ -2220,23 +3336,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F49" t="n">
-        <v>19247.57853232534</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G49" t="n">
-        <v>14750.76208031789</v>
+        <v>0.55</v>
       </c>
       <c r="H49" t="n">
-        <v>4496.81645200745</v>
+        <v>0.79</v>
       </c>
       <c r="I49" t="n">
-        <v>23.36302431215061</v>
+        <v>24020.85729436327</v>
+      </c>
+      <c r="J49" t="n">
+        <v>19704.90867882171</v>
+      </c>
+      <c r="K49" t="n">
+        <v>9488.324155134174</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4315.948615541558</v>
+      </c>
+      <c r="M49" t="n">
+        <v>17.96750450099189</v>
+      </c>
+      <c r="N49" t="n">
+        <v>11.08726543624516</v>
+      </c>
+      <c r="O49" t="n">
+        <v>25.70777344883196</v>
+      </c>
+      <c r="P49" t="n">
+        <v>34.30807227976538</v>
       </c>
     </row>
     <row r="50">
@@ -2257,23 +3396,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F50" t="n">
-        <v>17703.65512064149</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G50" t="n">
-        <v>10852.71813155156</v>
+        <v>0.55</v>
       </c>
       <c r="H50" t="n">
-        <v>6850.936989089929</v>
+        <v>0.83</v>
       </c>
       <c r="I50" t="n">
-        <v>38.69786743135384</v>
+        <v>13837.32067332521</v>
+      </c>
+      <c r="J50" t="n">
+        <v>12915.92005202739</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6105.272240206291</v>
+      </c>
+      <c r="L50" t="n">
+        <v>921.4006212978202</v>
+      </c>
+      <c r="M50" t="n">
+        <v>6.658808038423533</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-0.4826785537526659</v>
+      </c>
+      <c r="O50" t="n">
+        <v>14.82050700091062</v>
+      </c>
+      <c r="P50" t="n">
+        <v>30.12369255557393</v>
       </c>
     </row>
     <row r="51">
@@ -2294,23 +3456,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F51" t="n">
-        <v>19474.02063270564</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G51" t="n">
-        <v>10852.71813155156</v>
+        <v>0.55</v>
       </c>
       <c r="H51" t="n">
-        <v>8621.302501154081</v>
+        <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>44.27078857395805</v>
+        <v>15488.24374642091</v>
+      </c>
+      <c r="J51" t="n">
+        <v>13760.36720391584</v>
+      </c>
+      <c r="K51" t="n">
+        <v>6858.918623074479</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1727.876542505071</v>
+      </c>
+      <c r="M51" t="n">
+        <v>11.15605210503196</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.365411693273384</v>
+      </c>
+      <c r="O51" t="n">
+        <v>18.91678400418463</v>
+      </c>
+      <c r="P51" t="n">
+        <v>33.46815631509589</v>
       </c>
     </row>
     <row r="52">
@@ -2331,23 +3516,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F52" t="n">
-        <v>15048.10685254526</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G52" t="n">
-        <v>10852.71813155156</v>
+        <v>0.55</v>
       </c>
       <c r="H52" t="n">
-        <v>4195.388720993704</v>
+        <v>0.83</v>
       </c>
       <c r="I52" t="n">
-        <v>27.87984403688687</v>
+        <v>17536.05965316886</v>
+      </c>
+      <c r="J52" t="n">
+        <v>14807.82504021741</v>
+      </c>
+      <c r="K52" t="n">
+        <v>7793.746584504917</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2728.234612951444</v>
+      </c>
+      <c r="M52" t="n">
+        <v>15.55785431226244</v>
+      </c>
+      <c r="N52" t="n">
+        <v>9.110614318290224</v>
+      </c>
+      <c r="O52" t="n">
+        <v>22.92612859108781</v>
+      </c>
+      <c r="P52" t="n">
+        <v>36.7416428638854</v>
       </c>
     </row>
     <row r="53">
@@ -2368,23 +3576,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F53" t="n">
-        <v>17703.65512064149</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G53" t="n">
-        <v>11786.42912988489</v>
+        <v>0.55</v>
       </c>
       <c r="H53" t="n">
-        <v>5917.225990756595</v>
+        <v>0.83</v>
       </c>
       <c r="I53" t="n">
-        <v>33.42375317658236</v>
+        <v>15713.57333999187</v>
+      </c>
+      <c r="J53" t="n">
+        <v>14792.17271869405</v>
+      </c>
+      <c r="K53" t="n">
+        <v>6105.272240206291</v>
+      </c>
+      <c r="L53" t="n">
+        <v>921.4006212978202</v>
+      </c>
+      <c r="M53" t="n">
+        <v>5.863724318852459</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-0.425045136831743</v>
+      </c>
+      <c r="O53" t="n">
+        <v>13.05088941106298</v>
+      </c>
+      <c r="P53" t="n">
+        <v>26.52682395895772</v>
       </c>
     </row>
     <row r="54">
@@ -2405,23 +3636,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F54" t="n">
-        <v>19474.02063270564</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G54" t="n">
-        <v>11786.42912988489</v>
+        <v>0.55</v>
       </c>
       <c r="H54" t="n">
-        <v>7687.591502820747</v>
+        <v>0.83</v>
       </c>
       <c r="I54" t="n">
-        <v>39.47613925143852</v>
+        <v>17364.49641308757</v>
+      </c>
+      <c r="J54" t="n">
+        <v>15636.6198705825</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6858.918623074479</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1727.87654250507</v>
+      </c>
+      <c r="M54" t="n">
+        <v>9.950628577991894</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3.89372422617073</v>
+      </c>
+      <c r="O54" t="n">
+        <v>16.87280498007322</v>
+      </c>
+      <c r="P54" t="n">
+        <v>29.8518857339757</v>
       </c>
     </row>
     <row r="55">
@@ -2442,23 +3696,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F55" t="n">
-        <v>15048.10685254526</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G55" t="n">
-        <v>11786.42912988489</v>
+        <v>0.55</v>
       </c>
       <c r="H55" t="n">
-        <v>3261.67772266037</v>
+        <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>21.67500373715571</v>
+        <v>19412.31231983552</v>
+      </c>
+      <c r="J55" t="n">
+        <v>16684.07770688408</v>
+      </c>
+      <c r="K55" t="n">
+        <v>7793.746584504917</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2728.234612951444</v>
+      </c>
+      <c r="M55" t="n">
+        <v>14.05414547222039</v>
+      </c>
+      <c r="N55" t="n">
+        <v>8.230048720126163</v>
+      </c>
+      <c r="O55" t="n">
+        <v>20.71025604604234</v>
+      </c>
+      <c r="P55" t="n">
+        <v>33.19046337195852</v>
       </c>
     </row>
     <row r="56">
@@ -2479,23 +3756,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F56" t="n">
-        <v>11527.96147390608</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G56" t="n">
-        <v>7147.301943510316</v>
+        <v>0.3</v>
       </c>
       <c r="H56" t="n">
-        <v>4380.659530395767</v>
+        <v>0.87</v>
       </c>
       <c r="I56" t="n">
-        <v>38.00029641243626</v>
+        <v>17391.50998883192</v>
+      </c>
+      <c r="J56" t="n">
+        <v>17393.04372205156</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2272.97330708513</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-1.53373321964682</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-0.008818861735592352</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-3.272902463824368</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3.799278674034607</v>
+      </c>
+      <c r="P56" t="n">
+        <v>14.67955734766378</v>
       </c>
     </row>
     <row r="57">
@@ -2516,23 +3816,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F57" t="n">
-        <v>12680.75762129669</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G57" t="n">
-        <v>7147.301943510316</v>
+        <v>0.3</v>
       </c>
       <c r="H57" t="n">
-        <v>5533.455677786378</v>
+        <v>0.87</v>
       </c>
       <c r="I57" t="n">
-        <v>43.63663310221479</v>
+        <v>18466.52966433609</v>
+      </c>
+      <c r="J57" t="n">
+        <v>17732.74993951089</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2553.553442391721</v>
+      </c>
+      <c r="L57" t="n">
+        <v>733.7797248252064</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.973565895504098</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.7947131791008119</v>
+      </c>
+      <c r="O57" t="n">
+        <v>7.682227397974592</v>
+      </c>
+      <c r="P57" t="n">
+        <v>18.27840311931887</v>
       </c>
     </row>
     <row r="58">
@@ -2553,23 +3876,46 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F58" t="n">
-        <v>9798.767252820171</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G58" t="n">
-        <v>7147.301943510316</v>
+        <v>0.3</v>
       </c>
       <c r="H58" t="n">
-        <v>2651.465309309855</v>
+        <v>0.87</v>
       </c>
       <c r="I58" t="n">
-        <v>27.05917224992501</v>
+        <v>19799.99118500917</v>
+      </c>
+      <c r="J58" t="n">
+        <v>18154.12378004358</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2901.586899287395</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1645.867404965593</v>
+      </c>
+      <c r="M58" t="n">
+        <v>8.312465341962879</v>
+      </c>
+      <c r="N58" t="n">
+        <v>5.226473628517578</v>
+      </c>
+      <c r="O58" t="n">
+        <v>11.91278900764904</v>
+      </c>
+      <c r="P58" t="n">
+        <v>22.19942805246669</v>
       </c>
     </row>
     <row r="59">
@@ -2590,23 +3936,46 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3095.585787837294</v>
-      </c>
-      <c r="F59" t="n">
-        <v>11527.96147390608</v>
+        <v>2208.516344131201</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G59" t="n">
-        <v>8081.01294184365</v>
+        <v>0.3</v>
       </c>
       <c r="H59" t="n">
-        <v>3446.948532062434</v>
+        <v>0.87</v>
       </c>
       <c r="I59" t="n">
-        <v>29.90076380689434</v>
+        <v>17391.50998883192</v>
+      </c>
+      <c r="J59" t="n">
+        <v>17393.04372205156</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2272.97330708513</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-1.53373321964682</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-0.008818861735592352</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-3.272902463824368</v>
+      </c>
+      <c r="O59" t="n">
+        <v>3.799278674034607</v>
+      </c>
+      <c r="P59" t="n">
+        <v>14.67955734766378</v>
       </c>
     </row>
     <row r="60">
@@ -2627,23 +3996,46 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3405.144366621024</v>
-      </c>
-      <c r="F60" t="n">
-        <v>12680.75762129669</v>
+        <v>2481.139789699865</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G60" t="n">
-        <v>8081.01294184365</v>
+        <v>0.3</v>
       </c>
       <c r="H60" t="n">
-        <v>4599.744679453044</v>
+        <v>0.87</v>
       </c>
       <c r="I60" t="n">
-        <v>36.27342164263123</v>
+        <v>18466.52966433609</v>
+      </c>
+      <c r="J60" t="n">
+        <v>17732.74993951089</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2553.553442391721</v>
+      </c>
+      <c r="L60" t="n">
+        <v>733.7797248252064</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.973565895504098</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.7947131791008119</v>
+      </c>
+      <c r="O60" t="n">
+        <v>7.682227397974592</v>
+      </c>
+      <c r="P60" t="n">
+        <v>18.27840311931887</v>
       </c>
     </row>
     <row r="61">
@@ -2664,23 +4056,46 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2631.2479196617</v>
-      </c>
-      <c r="F61" t="n">
-        <v>9798.767252820171</v>
+        <v>2819.30371598208</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G61" t="n">
-        <v>8081.01294184365</v>
+        <v>0.3</v>
       </c>
       <c r="H61" t="n">
-        <v>1717.754310976521</v>
+        <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>17.53031036105217</v>
+        <v>19799.99118500917</v>
+      </c>
+      <c r="J61" t="n">
+        <v>18154.12378004358</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2901.586899287395</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1645.867404965593</v>
+      </c>
+      <c r="M61" t="n">
+        <v>8.312465341962879</v>
+      </c>
+      <c r="N61" t="n">
+        <v>5.226473628517578</v>
+      </c>
+      <c r="O61" t="n">
+        <v>11.91278900764904</v>
+      </c>
+      <c r="P61" t="n">
+        <v>22.19942805246669</v>
       </c>
     </row>
   </sheetData>
